--- a/plots/countries/sectors/United Kingdom-sectors.xlsx
+++ b/plots/countries/sectors/United Kingdom-sectors.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">Author</t>
   </si>
@@ -30,13 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2025). Tidy GHG Inventories (1.0) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14945466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See also</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
@@ -443,14 +437,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -464,6142 +450,6322 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
       </c>
       <c r="D2" t="n">
         <v>1990</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>50.6471823529948</v>
+        <v>51.1069998722623</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>1990</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>121.60196257293</v>
+        <v>120.97650993979</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
         <v>1990</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>45.0951630804078</v>
+        <v>45.0952196002285</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
         <v>1990</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>72.9766893174043</v>
+        <v>73.0900903216936</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>1990</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>239.586211928607</v>
+        <v>239.485847331926</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
         <v>1990</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>123.578787526784</v>
+        <v>120.43302047254</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>1990</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>80.1499699638577</v>
+        <v>80.3865516689821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
         <v>1990</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>10.6647724371143</v>
+        <v>10.3130606783574</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>1990</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>70.5155203369308</v>
+        <v>55.2733271247081</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
       </c>
       <c r="D11" t="n">
         <v>1991</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>50.289658527844</v>
+        <v>50.7454682532727</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>1991</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>132.441556815142</v>
+        <v>131.908023548968</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
         <v>1991</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>45.0068364405519</v>
+        <v>45.0068974246822</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
         <v>1991</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>76.3701777049506</v>
+        <v>76.4131737835192</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
         <v>1991</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>236.888410759529</v>
+        <v>236.780247549744</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
         <v>1991</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>122.637382265227</v>
+        <v>119.722603087311</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
         <v>1991</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>78.1890712082639</v>
+        <v>78.4255586228555</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
         <v>1991</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>10.1512205032887</v>
+        <v>9.81582411435066</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
         <v>1991</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>71.382377903072</v>
+        <v>57.0714410603758</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
         <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>1992</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>49.7572115741774</v>
+        <v>50.228126899286</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
         <v>1992</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>128.976616792177</v>
+        <v>128.28427660153</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
         <v>1992</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>44.864357969315</v>
+        <v>44.8644217962542</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D23" t="n">
         <v>1992</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>74.1471654065632</v>
+        <v>74.3090641337179</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
         <v>1992</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>226.023551455077</v>
+        <v>225.906633765194</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
         <v>1992</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>124.036437443022</v>
+        <v>121.151440068216</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
         <v>1992</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>73.4682530776662</v>
+        <v>73.7046679437855</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
         <v>1992</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>9.31291494122191</v>
+        <v>9.00226425816468</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D28" t="n">
         <v>1992</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>71.5395491933577</v>
+        <v>58.2342250430338</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
         <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" t="s">
-        <v>16</v>
       </c>
       <c r="D29" t="n">
         <v>1993</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>49.0964401647828</v>
+        <v>49.5677524936501</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
         <v>1993</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>132.542995598702</v>
+        <v>131.908649150153</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31" t="n">
         <v>1993</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>42.8172664742613</v>
+        <v>42.8173340876005</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D32" t="n">
         <v>1993</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>71.608006804162</v>
+        <v>71.6523512637121</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D33" t="n">
         <v>1993</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>210.144747420451</v>
+        <v>210.019671169425</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D34" t="n">
         <v>1993</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F34" t="n">
-        <v>125.309828011942</v>
+        <v>122.219883055944</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D35" t="n">
         <v>1993</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F35" t="n">
-        <v>70.0420158182131</v>
+        <v>70.2784323562199</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D36" t="n">
         <v>1993</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>8.7304472426455</v>
+        <v>8.44452138183261</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D37" t="n">
         <v>1993</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>72.2132663258773</v>
+        <v>59.7068891279821</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
         <v>14</v>
-      </c>
-      <c r="B38" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" t="s">
-        <v>16</v>
       </c>
       <c r="D38" t="n">
         <v>1994</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>49.8477730655277</v>
+        <v>50.3074087566337</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D39" t="n">
         <v>1994</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>127.293269607804</v>
+        <v>126.512916810679</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D40" t="n">
         <v>1994</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F40" t="n">
-        <v>35.5390331438452</v>
+        <v>35.5391043199936</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D41" t="n">
         <v>1994</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>70.6063518644441</v>
+        <v>70.7599768060126</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D42" t="n">
         <v>1994</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F42" t="n">
-        <v>205.819773828045</v>
+        <v>205.686387801875</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D43" t="n">
         <v>1994</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
-        <v>126.744321336337</v>
+        <v>122.580704267434</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D44" t="n">
         <v>1994</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F44" t="n">
-        <v>73.1770386600049</v>
+        <v>73.4135158872792</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D45" t="n">
         <v>1994</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F45" t="n">
-        <v>8.28644133198345</v>
+        <v>7.96560930532839</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D46" t="n">
         <v>1994</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>72.6895124788558</v>
+        <v>61.2097396306052</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
         <v>14</v>
-      </c>
-      <c r="B47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" t="s">
-        <v>16</v>
       </c>
       <c r="D47" t="n">
         <v>1995</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>49.6690332243214</v>
+        <v>50.133571801979</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D48" t="n">
         <v>1995</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>123.051087639127</v>
+        <v>122.075047112075</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D49" t="n">
         <v>1995</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F49" t="n">
-        <v>37.8585246916009</v>
+        <v>37.8585986419771</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D50" t="n">
         <v>1995</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F50" t="n">
-        <v>67.6366054516204</v>
+        <v>67.9185981068016</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D51" t="n">
         <v>1995</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F51" t="n">
-        <v>203.734635640309</v>
+        <v>203.593148517541</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D52" t="n">
         <v>1995</v>
       </c>
       <c r="E52" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F52" t="n">
-        <v>126.222145987014</v>
+        <v>121.594730597693</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D53" t="n">
         <v>1995</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F53" t="n">
-        <v>73.5454031485059</v>
+        <v>73.781860850633</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D54" t="n">
         <v>1995</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F54" t="n">
-        <v>8.3244875884708</v>
+        <v>7.99407157470638</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D55" t="n">
         <v>1995</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F55" t="n">
-        <v>73.4050709690949</v>
+        <v>63.1979869508897</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
         <v>14</v>
-      </c>
-      <c r="B56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C56" t="s">
-        <v>16</v>
       </c>
       <c r="D56" t="n">
         <v>1996</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
-        <v>50.6400073372167</v>
+        <v>51.1236692921205</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D57" t="n">
         <v>1996</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>136.443102593125</v>
+        <v>135.642250588891</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D58" t="n">
         <v>1996</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F58" t="n">
-        <v>36.4584036277237</v>
+        <v>36.4584902450183</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D59" t="n">
         <v>1996</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F59" t="n">
-        <v>67.0861376432526</v>
+        <v>67.28807700873</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D60" t="n">
         <v>1996</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F60" t="n">
-        <v>204.76416521162</v>
+        <v>204.614515960827</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D61" t="n">
         <v>1996</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F61" t="n">
-        <v>130.7295343849</v>
+        <v>126.496729534761</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D62" t="n">
         <v>1996</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F62" t="n">
-        <v>75.937307949734</v>
+        <v>76.0956385447759</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D63" t="n">
         <v>1996</v>
       </c>
       <c r="E63" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F63" t="n">
-        <v>7.32837523518685</v>
+        <v>6.99254643631051</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D64" t="n">
         <v>1996</v>
       </c>
       <c r="E64" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>74.0478039998027</v>
+        <v>64.4169538046269</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
         <v>14</v>
-      </c>
-      <c r="B65" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65" t="s">
-        <v>16</v>
       </c>
       <c r="D65" t="n">
         <v>1997</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F65" t="n">
-        <v>50.5200749687912</v>
+        <v>51.0059687045553</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D66" t="n">
         <v>1997</v>
       </c>
       <c r="E66" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F66" t="n">
-        <v>126.50565360216</v>
+        <v>125.7409096776</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D67" t="n">
         <v>1997</v>
       </c>
       <c r="E67" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F67" t="n">
-        <v>32.7986302909828</v>
+        <v>32.7987134904467</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D68" t="n">
         <v>1997</v>
       </c>
       <c r="E68" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F68" t="n">
-        <v>66.7057413237619</v>
+        <v>66.913567406349</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D69" t="n">
         <v>1997</v>
       </c>
       <c r="E69" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>193.90562535648</v>
+        <v>193.747844509182</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D70" t="n">
         <v>1997</v>
       </c>
       <c r="E70" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F70" t="n">
-        <v>131.409836515782</v>
+        <v>127.106266402655</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D71" t="n">
         <v>1997</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F71" t="n">
-        <v>76.5249687676874</v>
+        <v>76.6610152006088</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D72" t="n">
         <v>1997</v>
       </c>
       <c r="E72" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F72" t="n">
-        <v>6.77903352890986</v>
+        <v>6.44794198144441</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D73" t="n">
         <v>1997</v>
       </c>
       <c r="E73" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F73" t="n">
-        <v>73.6349009120138</v>
+        <v>64.9262502115755</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
         <v>14</v>
-      </c>
-      <c r="B74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" t="s">
-        <v>16</v>
       </c>
       <c r="D74" t="n">
         <v>1998</v>
       </c>
       <c r="E74" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F74" t="n">
-        <v>50.3321168103143</v>
+        <v>50.8132216952094</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D75" t="n">
         <v>1998</v>
       </c>
       <c r="E75" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F75" t="n">
-        <v>127.112286122504</v>
+        <v>127.166390402406</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D76" t="n">
         <v>1998</v>
       </c>
       <c r="E76" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F76" t="n">
-        <v>30.6558813715721</v>
+        <v>30.6692512139791</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D77" t="n">
         <v>1998</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F77" t="n">
-        <v>68.1547128894177</v>
+        <v>67.5760846529278</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D78" t="n">
         <v>1998</v>
       </c>
       <c r="E78" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>199.445293659814</v>
+        <v>199.279480037175</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D79" t="n">
         <v>1998</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
-        <v>130.907381067877</v>
+        <v>126.913516480169</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D80" t="n">
         <v>1998</v>
       </c>
       <c r="E80" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>71.2258293036659</v>
+        <v>71.3434626320379</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D81" t="n">
         <v>1998</v>
       </c>
       <c r="E81" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F81" t="n">
-        <v>5.99149476243992</v>
+        <v>5.66273407402704</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D82" t="n">
         <v>1998</v>
       </c>
       <c r="E82" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
-        <v>73.2279014980814</v>
+        <v>65.2994626181449</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" t="s">
         <v>14</v>
-      </c>
-      <c r="B83" t="s">
-        <v>15</v>
-      </c>
-      <c r="C83" t="s">
-        <v>16</v>
       </c>
       <c r="D83" t="n">
         <v>1999</v>
       </c>
       <c r="E83" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F83" t="n">
-        <v>50.1161068885997</v>
+        <v>50.5971086297224</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D84" t="n">
         <v>1999</v>
       </c>
       <c r="E84" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F84" t="n">
-        <v>128.561721842425</v>
+        <v>128.722375314075</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D85" t="n">
         <v>1999</v>
       </c>
       <c r="E85" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F85" t="n">
-        <v>26.2951403075062</v>
+        <v>26.2952289103634</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D86" t="n">
         <v>1999</v>
       </c>
       <c r="E86" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F86" t="n">
-        <v>67.8519410947027</v>
+        <v>67.1778851111006</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D87" t="n">
         <v>1999</v>
       </c>
       <c r="E87" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F87" t="n">
-        <v>190.096985361101</v>
+        <v>189.923047901967</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D88" t="n">
         <v>1999</v>
       </c>
       <c r="E88" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F88" t="n">
-        <v>132.50870278307</v>
+        <v>127.565360020401</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D89" t="n">
         <v>1999</v>
       </c>
       <c r="E89" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F89" t="n">
-        <v>56.5947707734064</v>
+        <v>56.6930309583878</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D90" t="n">
         <v>1999</v>
       </c>
       <c r="E90" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F90" t="n">
-        <v>6.10670825317125</v>
+        <v>5.78400277263302</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D91" t="n">
         <v>1999</v>
       </c>
       <c r="E91" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F91" t="n">
-        <v>70.7037968780228</v>
+        <v>63.6383024500635</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" t="s">
         <v>14</v>
-      </c>
-      <c r="B92" t="s">
-        <v>15</v>
-      </c>
-      <c r="C92" t="s">
-        <v>16</v>
       </c>
       <c r="D92" t="n">
         <v>2000</v>
       </c>
       <c r="E92" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F92" t="n">
-        <v>48.3534704704006</v>
+        <v>48.8175840239565</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D93" t="n">
         <v>2000</v>
       </c>
       <c r="E93" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F93" t="n">
-        <v>127.482054723456</v>
+        <v>127.825621457193</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D94" t="n">
         <v>2000</v>
       </c>
       <c r="E94" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
-        <v>24.7054566297223</v>
+        <v>24.7055485160495</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D95" t="n">
         <v>2000</v>
       </c>
       <c r="E95" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F95" t="n">
-        <v>69.8011062868395</v>
+        <v>68.9714142969372</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D96" t="n">
         <v>2000</v>
       </c>
       <c r="E96" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
-        <v>200.967051530826</v>
+        <v>200.783745098025</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D97" t="n">
         <v>2000</v>
       </c>
       <c r="E97" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F97" t="n">
-        <v>130.801345030974</v>
+        <v>126.423030931596</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D98" t="n">
         <v>2000</v>
       </c>
       <c r="E98" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F98" t="n">
-        <v>52.8543110037908</v>
+        <v>52.9717228130861</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D99" t="n">
         <v>2000</v>
       </c>
       <c r="E99" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F99" t="n">
-        <v>5.84661017958988</v>
+        <v>5.53578018036298</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D100" t="n">
         <v>2000</v>
       </c>
       <c r="E100" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F100" t="n">
-        <v>67.9126290532173</v>
+        <v>61.7001385401106</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" t="s">
         <v>14</v>
-      </c>
-      <c r="B101" t="s">
-        <v>15</v>
-      </c>
-      <c r="C101" t="s">
-        <v>16</v>
       </c>
       <c r="D101" t="n">
         <v>2001</v>
       </c>
       <c r="E101" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F101" t="n">
-        <v>46.0405854887592</v>
+        <v>46.4728673599559</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D102" t="n">
         <v>2001</v>
       </c>
       <c r="E102" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F102" t="n">
-        <v>130.445493161022</v>
+        <v>130.602335387098</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D103" t="n">
         <v>2001</v>
       </c>
       <c r="E103" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F103" t="n">
-        <v>23.3403600087972</v>
+        <v>23.3404528438925</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D104" t="n">
         <v>2001</v>
       </c>
       <c r="E104" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F104" t="n">
-        <v>68.0806584303736</v>
+        <v>67.4161769019376</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D105" t="n">
         <v>2001</v>
       </c>
       <c r="E105" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F105" t="n">
-        <v>211.996445193622</v>
+        <v>211.802208424189</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D106" t="n">
         <v>2001</v>
       </c>
       <c r="E106" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F106" t="n">
-        <v>130.750654046121</v>
+        <v>126.377479916443</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D107" t="n">
         <v>2001</v>
       </c>
       <c r="E107" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F107" t="n">
-        <v>49.5321996514555</v>
+        <v>49.6493818444894</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D108" t="n">
         <v>2001</v>
       </c>
       <c r="E108" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F108" t="n">
-        <v>5.2049237666997</v>
+        <v>4.90316594943232</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D109" t="n">
         <v>2001</v>
       </c>
       <c r="E109" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F109" t="n">
-        <v>65.5916026943288</v>
+        <v>60.774884534053</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" t="s">
         <v>14</v>
-      </c>
-      <c r="B110" t="s">
-        <v>15</v>
-      </c>
-      <c r="C110" t="s">
-        <v>16</v>
       </c>
       <c r="D110" t="n">
         <v>2002</v>
       </c>
       <c r="E110" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F110" t="n">
-        <v>45.4977681993629</v>
+        <v>45.9166812968612</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D111" t="n">
         <v>2002</v>
       </c>
       <c r="E111" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F111" t="n">
-        <v>122.576905945443</v>
+        <v>122.310744728316</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D112" t="n">
         <v>2002</v>
       </c>
       <c r="E112" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>22.2972479493827</v>
+        <v>22.2973451375186</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D113" t="n">
         <v>2002</v>
       </c>
       <c r="E113" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F113" t="n">
-        <v>61.5802348929501</v>
+        <v>61.2954856733285</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D114" t="n">
         <v>2002</v>
       </c>
       <c r="E114" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F114" t="n">
-        <v>208.929050645451</v>
+        <v>208.726738811355</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D115" t="n">
         <v>2002</v>
       </c>
       <c r="E115" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F115" t="n">
-        <v>133.569509187759</v>
+        <v>128.296561385962</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D116" t="n">
         <v>2002</v>
       </c>
       <c r="E116" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F116" t="n">
-        <v>45.8796056922427</v>
+        <v>45.9771727158949</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D117" t="n">
         <v>2002</v>
       </c>
       <c r="E117" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F117" t="n">
-        <v>4.37488858346897</v>
+        <v>4.0920232493789</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D118" t="n">
         <v>2002</v>
       </c>
       <c r="E118" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F118" t="n">
-        <v>65.1321198893289</v>
+        <v>61.0590542712799</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>12</v>
+      </c>
+      <c r="B119" t="s">
+        <v>13</v>
+      </c>
+      <c r="C119" t="s">
         <v>14</v>
-      </c>
-      <c r="B119" t="s">
-        <v>15</v>
-      </c>
-      <c r="C119" t="s">
-        <v>16</v>
       </c>
       <c r="D119" t="n">
         <v>2003</v>
       </c>
       <c r="E119" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F119" t="n">
-        <v>45.8842252060941</v>
+        <v>46.2985153849487</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D120" t="n">
         <v>2003</v>
       </c>
       <c r="E120" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F120" t="n">
-        <v>123.319409060184</v>
+        <v>123.283736573825</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D121" t="n">
         <v>2003</v>
       </c>
       <c r="E121" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F121" t="n">
-        <v>20.0383847166484</v>
+        <v>20.0384846190739</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C122" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D122" t="n">
         <v>2003</v>
       </c>
       <c r="E122" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F122" t="n">
-        <v>61.9172299109759</v>
+        <v>61.4498734072436</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C123" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D123" t="n">
         <v>2003</v>
       </c>
       <c r="E123" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F123" t="n">
-        <v>216.647766568114</v>
+        <v>216.436102814375</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D124" t="n">
         <v>2003</v>
       </c>
       <c r="E124" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F124" t="n">
-        <v>132.855251949305</v>
+        <v>129.137763642006</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D125" t="n">
         <v>2003</v>
       </c>
       <c r="E125" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F125" t="n">
-        <v>49.2674279902332</v>
+        <v>49.3652327415419</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C126" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D126" t="n">
         <v>2003</v>
       </c>
       <c r="E126" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F126" t="n">
-        <v>4.21586132110495</v>
+        <v>3.95508990598712</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D127" t="n">
         <v>2003</v>
       </c>
       <c r="E127" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F127" t="n">
-        <v>61.6839958623105</v>
+        <v>58.0693682444125</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
+        <v>12</v>
+      </c>
+      <c r="B128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" t="s">
         <v>14</v>
-      </c>
-      <c r="B128" t="s">
-        <v>15</v>
-      </c>
-      <c r="C128" t="s">
-        <v>16</v>
       </c>
       <c r="D128" t="n">
         <v>2004</v>
       </c>
       <c r="E128" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F128" t="n">
-        <v>46.271368789993</v>
+        <v>46.6931330291304</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C129" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D129" t="n">
         <v>2004</v>
       </c>
       <c r="E129" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F129" t="n">
-        <v>125.959077943147</v>
+        <v>125.914709912465</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D130" t="n">
         <v>2004</v>
       </c>
       <c r="E130" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F130" t="n">
-        <v>19.8254883043176</v>
+        <v>19.8255909410295</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C131" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D131" t="n">
         <v>2004</v>
       </c>
       <c r="E131" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F131" t="n">
-        <v>59.9758322172949</v>
+        <v>59.4910395874767</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C132" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D132" t="n">
         <v>2004</v>
       </c>
       <c r="E132" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F132" t="n">
-        <v>214.842188521739</v>
+        <v>214.641904948816</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C133" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D133" t="n">
         <v>2004</v>
       </c>
       <c r="E133" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F133" t="n">
-        <v>134.164161310197</v>
+        <v>130.547007900905</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D134" t="n">
         <v>2004</v>
       </c>
       <c r="E134" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F134" t="n">
-        <v>50.4878554247805</v>
+        <v>50.6049185553031</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C135" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D135" t="n">
         <v>2004</v>
       </c>
       <c r="E135" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F135" t="n">
-        <v>3.36438759920793</v>
+        <v>3.11344851275115</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D136" t="n">
         <v>2004</v>
       </c>
       <c r="E136" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F136" t="n">
-        <v>57.0042367856025</v>
+        <v>53.8358385202949</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137" t="s">
         <v>14</v>
-      </c>
-      <c r="B137" t="s">
-        <v>15</v>
-      </c>
-      <c r="C137" t="s">
-        <v>16</v>
       </c>
       <c r="D137" t="n">
         <v>2005</v>
       </c>
       <c r="E137" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F137" t="n">
-        <v>46.2519897721436</v>
+        <v>46.6992648653707</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C138" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D138" t="n">
         <v>2005</v>
       </c>
       <c r="E138" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F138" t="n">
-        <v>121.525512591</v>
+        <v>121.363366004618</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C139" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D139" t="n">
         <v>2005</v>
       </c>
       <c r="E139" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F139" t="n">
-        <v>18.2310403662139</v>
+        <v>18.2311473718731</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C140" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D140" t="n">
         <v>2005</v>
       </c>
       <c r="E140" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F140" t="n">
-        <v>60.7803571259538</v>
+        <v>60.4578990676954</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C141" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D141" t="n">
         <v>2005</v>
       </c>
       <c r="E141" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F141" t="n">
-        <v>215.146619009193</v>
+        <v>214.957697360602</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C142" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D142" t="n">
         <v>2005</v>
       </c>
       <c r="E142" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F142" t="n">
-        <v>134.663166881122</v>
+        <v>131.661412064262</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C143" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D143" t="n">
         <v>2005</v>
       </c>
       <c r="E143" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F143" t="n">
-        <v>49.3176862154433</v>
+        <v>49.4346984999093</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C144" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D144" t="n">
         <v>2005</v>
       </c>
       <c r="E144" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F144" t="n">
-        <v>2.99479575925358</v>
+        <v>2.72828302281841</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C145" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D145" t="n">
         <v>2005</v>
       </c>
       <c r="E145" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F145" t="n">
-        <v>54.7511244721121</v>
+        <v>52.0148278704498</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
+        <v>12</v>
+      </c>
+      <c r="B146" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" t="s">
         <v>14</v>
-      </c>
-      <c r="B146" t="s">
-        <v>15</v>
-      </c>
-      <c r="C146" t="s">
-        <v>16</v>
       </c>
       <c r="D146" t="n">
         <v>2006</v>
       </c>
       <c r="E146" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F146" t="n">
-        <v>45.2376347666298</v>
+        <v>45.6773549557401</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C147" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D147" t="n">
         <v>2006</v>
       </c>
       <c r="E147" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F147" t="n">
-        <v>117.094983829325</v>
+        <v>117.080776741464</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C148" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D148" t="n">
         <v>2006</v>
       </c>
       <c r="E148" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F148" t="n">
-        <v>16.6074631254457</v>
+        <v>16.6075732165286</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C149" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D149" t="n">
         <v>2006</v>
       </c>
       <c r="E149" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F149" t="n">
-        <v>57.9346588997172</v>
+        <v>57.6231068201279</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C150" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D150" t="n">
         <v>2006</v>
       </c>
       <c r="E150" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F150" t="n">
-        <v>221.181106243103</v>
+        <v>220.991095706624</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C151" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D151" t="n">
         <v>2006</v>
       </c>
       <c r="E151" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F151" t="n">
-        <v>134.103508227349</v>
+        <v>132.802760441056</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C152" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D152" t="n">
         <v>2006</v>
       </c>
       <c r="E152" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F152" t="n">
-        <v>49.8230298164236</v>
+        <v>49.9400831023159</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C153" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D153" t="n">
         <v>2006</v>
       </c>
       <c r="E153" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F153" t="n">
-        <v>2.58417566317645</v>
+        <v>2.28125438581629</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C154" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D154" t="n">
         <v>2006</v>
       </c>
       <c r="E154" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F154" t="n">
-        <v>52.7793144662384</v>
+        <v>50.7077621772193</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
+        <v>12</v>
+      </c>
+      <c r="B155" t="s">
+        <v>13</v>
+      </c>
+      <c r="C155" t="s">
         <v>14</v>
-      </c>
-      <c r="B155" t="s">
-        <v>15</v>
-      </c>
-      <c r="C155" t="s">
-        <v>16</v>
       </c>
       <c r="D155" t="n">
         <v>2007</v>
       </c>
       <c r="E155" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F155" t="n">
-        <v>44.8134144746045</v>
+        <v>45.251467460001</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C156" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D156" t="n">
         <v>2007</v>
       </c>
       <c r="E156" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F156" t="n">
-        <v>112.422826491945</v>
+        <v>112.305149575949</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C157" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D157" t="n">
         <v>2007</v>
       </c>
       <c r="E157" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F157" t="n">
-        <v>16.2729595923652</v>
+        <v>16.2730713488276</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C158" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D158" t="n">
         <v>2007</v>
       </c>
       <c r="E158" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F158" t="n">
-        <v>56.8189992545428</v>
+        <v>56.5669299365978</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C159" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D159" t="n">
         <v>2007</v>
       </c>
       <c r="E159" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F159" t="n">
-        <v>216.080710208086</v>
+        <v>215.888693485434</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C160" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D160" t="n">
         <v>2007</v>
       </c>
       <c r="E160" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F160" t="n">
-        <v>134.895425683609</v>
+        <v>132.86824000207</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C161" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D161" t="n">
         <v>2007</v>
       </c>
       <c r="E161" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F161" t="n">
-        <v>51.809667612838</v>
+        <v>51.92212585555</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C162" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D162" t="n">
         <v>2007</v>
       </c>
       <c r="E162" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F162" t="n">
-        <v>2.15601354642002</v>
+        <v>1.89838786587908</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C163" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D163" t="n">
         <v>2007</v>
       </c>
       <c r="E163" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F163" t="n">
-        <v>49.1876372284189</v>
+        <v>47.7225871222307</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
+        <v>12</v>
+      </c>
+      <c r="B164" t="s">
+        <v>13</v>
+      </c>
+      <c r="C164" t="s">
         <v>14</v>
-      </c>
-      <c r="B164" t="s">
-        <v>15</v>
-      </c>
-      <c r="C164" t="s">
-        <v>16</v>
       </c>
       <c r="D164" t="n">
         <v>2008</v>
       </c>
       <c r="E164" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F164" t="n">
-        <v>43.7608563015123</v>
+        <v>44.1798819355351</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C165" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D165" t="n">
         <v>2008</v>
       </c>
       <c r="E165" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F165" t="n">
-        <v>117.149569776561</v>
+        <v>116.957530446873</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C166" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D166" t="n">
         <v>2008</v>
       </c>
       <c r="E166" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F166" t="n">
-        <v>15.1338882657664</v>
+        <v>15.1340035342452</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C167" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D167" t="n">
         <v>2008</v>
       </c>
       <c r="E167" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F167" t="n">
-        <v>51.3711067959059</v>
+        <v>51.1811671402949</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C168" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D168" t="n">
         <v>2008</v>
       </c>
       <c r="E168" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F168" t="n">
-        <v>210.44606789381</v>
+        <v>210.258596699466</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C169" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D169" t="n">
         <v>2008</v>
       </c>
       <c r="E169" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F169" t="n">
-        <v>130.038538401103</v>
+        <v>127.165854597884</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C170" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D170" t="n">
         <v>2008</v>
       </c>
       <c r="E170" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F170" t="n">
-        <v>49.1459024030646</v>
+        <v>49.2539641186449</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C171" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D171" t="n">
         <v>2008</v>
       </c>
       <c r="E171" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F171" t="n">
-        <v>1.40836725323564</v>
+        <v>1.16923360234789</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C172" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D172" t="n">
         <v>2008</v>
       </c>
       <c r="E172" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F172" t="n">
-        <v>44.3212436976013</v>
+        <v>43.3166911229967</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
+        <v>12</v>
+      </c>
+      <c r="B173" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173" t="s">
         <v>14</v>
-      </c>
-      <c r="B173" t="s">
-        <v>15</v>
-      </c>
-      <c r="C173" t="s">
-        <v>16</v>
       </c>
       <c r="D173" t="n">
         <v>2009</v>
       </c>
       <c r="E173" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F173" t="n">
-        <v>43.412350713487</v>
+        <v>43.8333103143455</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D174" t="n">
         <v>2009</v>
       </c>
       <c r="E174" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F174" t="n">
-        <v>109.458697400234</v>
+        <v>109.240783365336</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C175" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D175" t="n">
         <v>2009</v>
       </c>
       <c r="E175" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F175" t="n">
-        <v>15.0953691637688</v>
+        <v>15.0953873088577</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C176" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D176" t="n">
         <v>2009</v>
       </c>
       <c r="E176" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F176" t="n">
-        <v>44.2008802215079</v>
+        <v>44.1537371879062</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C177" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D177" t="n">
         <v>2009</v>
       </c>
       <c r="E177" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F177" t="n">
-        <v>187.195606376283</v>
+        <v>187.014599450266</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C178" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D178" t="n">
         <v>2009</v>
       </c>
       <c r="E178" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F178" t="n">
-        <v>125.62717904327</v>
+        <v>122.889866719542</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C179" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D179" t="n">
         <v>2009</v>
       </c>
       <c r="E179" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F179" t="n">
-        <v>39.3931883526968</v>
+        <v>39.4886179715419</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C180" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D180" t="n">
         <v>2009</v>
       </c>
       <c r="E180" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F180" t="n">
-        <v>1.30424090080131</v>
+        <v>1.06593724815603</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C181" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D181" t="n">
         <v>2009</v>
       </c>
       <c r="E181" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F181" t="n">
-        <v>40.2495301195956</v>
+        <v>39.7271695518025</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
+        <v>12</v>
+      </c>
+      <c r="B182" t="s">
+        <v>13</v>
+      </c>
+      <c r="C182" t="s">
         <v>14</v>
-      </c>
-      <c r="B182" t="s">
-        <v>15</v>
-      </c>
-      <c r="C182" t="s">
-        <v>16</v>
       </c>
       <c r="D182" t="n">
         <v>2010</v>
       </c>
       <c r="E182" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F182" t="n">
-        <v>43.742935429872</v>
+        <v>44.1693441552375</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C183" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D183" t="n">
         <v>2010</v>
       </c>
       <c r="E183" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F183" t="n">
-        <v>120.200826784522</v>
+        <v>120.238891191552</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C184" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D184" t="n">
         <v>2010</v>
       </c>
       <c r="E184" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F184" t="n">
-        <v>14.6820216477321</v>
+        <v>14.6820386411893</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C185" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D185" t="n">
         <v>2010</v>
       </c>
       <c r="E185" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F185" t="n">
-        <v>46.6551817028404</v>
+        <v>46.2782643011518</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C186" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D186" t="n">
         <v>2010</v>
       </c>
       <c r="E186" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F186" t="n">
-        <v>194.535296499749</v>
+        <v>194.369046126606</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C187" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D187" t="n">
         <v>2010</v>
       </c>
       <c r="E187" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F187" t="n">
-        <v>124.006609892957</v>
+        <v>121.345993304692</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C188" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D188" t="n">
         <v>2010</v>
       </c>
       <c r="E188" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F188" t="n">
-        <v>40.3574149711566</v>
+        <v>40.4684505719092</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C189" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D189" t="n">
         <v>2010</v>
       </c>
       <c r="E189" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F189" t="n">
-        <v>1.21186671657399</v>
+        <v>0.973506103779758</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C190" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D190" t="n">
         <v>2010</v>
       </c>
       <c r="E190" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F190" t="n">
-        <v>35.0019159481571</v>
+        <v>35.0217342369415</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
+        <v>12</v>
+      </c>
+      <c r="B191" t="s">
+        <v>13</v>
+      </c>
+      <c r="C191" t="s">
         <v>14</v>
-      </c>
-      <c r="B191" t="s">
-        <v>15</v>
-      </c>
-      <c r="C191" t="s">
-        <v>16</v>
       </c>
       <c r="D191" t="n">
         <v>2011</v>
       </c>
       <c r="E191" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F191" t="n">
-        <v>43.5945746026794</v>
+        <v>44.0289722117024</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C192" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D192" t="n">
         <v>2011</v>
       </c>
       <c r="E192" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F192" t="n">
-        <v>99.0026270332738</v>
+        <v>98.7499203988642</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C193" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D193" t="n">
         <v>2011</v>
       </c>
       <c r="E193" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F193" t="n">
-        <v>14.0905795020605</v>
+        <v>14.0905942901878</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C194" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D194" t="n">
         <v>2011</v>
       </c>
       <c r="E194" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F194" t="n">
-        <v>45.0387566079095</v>
+        <v>45.0104825280777</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C195" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D195" t="n">
         <v>2011</v>
       </c>
       <c r="E195" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F195" t="n">
-        <v>180.219334261577</v>
+        <v>180.096619143993</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C196" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D196" t="n">
         <v>2011</v>
       </c>
       <c r="E196" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F196" t="n">
-        <v>121.454699391596</v>
+        <v>119.316781065025</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C197" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D197" t="n">
         <v>2011</v>
       </c>
       <c r="E197" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F197" t="n">
-        <v>38.4172861327613</v>
+        <v>38.5608728665139</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C198" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D198" t="n">
         <v>2011</v>
       </c>
       <c r="E198" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F198" t="n">
-        <v>0.563572599967668</v>
+        <v>0.335376575361832</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C199" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D199" t="n">
         <v>2011</v>
       </c>
       <c r="E199" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F199" t="n">
-        <v>32.697233855713</v>
+        <v>33.117962756976</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
+        <v>12</v>
+      </c>
+      <c r="B200" t="s">
+        <v>13</v>
+      </c>
+      <c r="C200" t="s">
         <v>14</v>
-      </c>
-      <c r="B200" t="s">
-        <v>15</v>
-      </c>
-      <c r="C200" t="s">
-        <v>16</v>
       </c>
       <c r="D200" t="n">
         <v>2012</v>
       </c>
       <c r="E200" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F200" t="n">
-        <v>43.2982225839716</v>
+        <v>43.7209242309969</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C201" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D201" t="n">
         <v>2012</v>
       </c>
       <c r="E201" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F201" t="n">
-        <v>108.791435074164</v>
+        <v>108.557177215541</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C202" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D202" t="n">
         <v>2012</v>
       </c>
       <c r="E202" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F202" t="n">
-        <v>13.2804481513556</v>
+        <v>13.2804389327803</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C203" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D203" t="n">
         <v>2012</v>
       </c>
       <c r="E203" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F203" t="n">
-        <v>42.5710305209084</v>
+        <v>42.5492758912294</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C204" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D204" t="n">
         <v>2012</v>
       </c>
       <c r="E204" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F204" t="n">
-        <v>191.333436467559</v>
+        <v>191.214941110871</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C205" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D205" t="n">
         <v>2012</v>
       </c>
       <c r="E205" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F205" t="n">
-        <v>120.850141819415</v>
+        <v>119.313801996807</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C206" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D206" t="n">
         <v>2012</v>
       </c>
       <c r="E206" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F206" t="n">
-        <v>39.7634476224297</v>
+        <v>39.8989586678469</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C207" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D207" t="n">
         <v>2012</v>
       </c>
       <c r="E207" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F207" t="n">
-        <v>0.666432760578476</v>
+        <v>0.425405623654037</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C208" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D208" t="n">
         <v>2012</v>
       </c>
       <c r="E208" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F208" t="n">
-        <v>30.9611868005523</v>
+        <v>31.5218735386688</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
+        <v>12</v>
+      </c>
+      <c r="B209" t="s">
+        <v>13</v>
+      </c>
+      <c r="C209" t="s">
         <v>14</v>
-      </c>
-      <c r="B209" t="s">
-        <v>15</v>
-      </c>
-      <c r="C209" t="s">
-        <v>16</v>
       </c>
       <c r="D209" t="n">
         <v>2013</v>
       </c>
       <c r="E209" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F209" t="n">
-        <v>43.0218006651886</v>
+        <v>43.446998271716</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C210" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D210" t="n">
         <v>2013</v>
       </c>
       <c r="E210" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F210" t="n">
-        <v>109.787606424947</v>
+        <v>109.558873147621</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C211" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D211" t="n">
         <v>2013</v>
       </c>
       <c r="E211" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F211" t="n">
-        <v>12.490957488935</v>
+        <v>12.4909695211613</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C212" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D212" t="n">
         <v>2013</v>
       </c>
       <c r="E212" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F212" t="n">
-        <v>42.5498309991889</v>
+        <v>42.4764664916678</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C213" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D213" t="n">
         <v>2013</v>
       </c>
       <c r="E213" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F213" t="n">
-        <v>179.163902990609</v>
+        <v>179.048280169379</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C214" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D214" t="n">
         <v>2013</v>
       </c>
       <c r="E214" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F214" t="n">
-        <v>119.305552646487</v>
+        <v>118.478234219131</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C215" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D215" t="n">
         <v>2013</v>
       </c>
       <c r="E215" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F215" t="n">
-        <v>44.1459392630163</v>
+        <v>44.3011545563005</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C216" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D216" t="n">
         <v>2013</v>
       </c>
       <c r="E216" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F216" t="n">
-        <v>0.559309430609775</v>
+        <v>0.292438733666205</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C217" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D217" t="n">
         <v>2013</v>
       </c>
       <c r="E217" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F217" t="n">
-        <v>27.5715306387512</v>
+        <v>28.3480296264843</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
+        <v>12</v>
+      </c>
+      <c r="B218" t="s">
+        <v>13</v>
+      </c>
+      <c r="C218" t="s">
         <v>14</v>
-      </c>
-      <c r="B218" t="s">
-        <v>15</v>
-      </c>
-      <c r="C218" t="s">
-        <v>16</v>
       </c>
       <c r="D218" t="n">
         <v>2014</v>
       </c>
       <c r="E218" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F218" t="n">
-        <v>44.3645106447715</v>
+        <v>44.8140007081586</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C219" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D219" t="n">
         <v>2014</v>
       </c>
       <c r="E219" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F219" t="n">
-        <v>93.6874111333726</v>
+        <v>93.3676233199019</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C220" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D220" t="n">
         <v>2014</v>
       </c>
       <c r="E220" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F220" t="n">
-        <v>12.2321527137601</v>
+        <v>12.2321631167848</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B221" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C221" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D221" t="n">
         <v>2014</v>
       </c>
       <c r="E221" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F221" t="n">
-        <v>40.5019480114478</v>
+        <v>40.5570332063054</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B222" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C222" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D222" t="n">
         <v>2014</v>
       </c>
       <c r="E222" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F222" t="n">
-        <v>154.407306150426</v>
+        <v>154.294831925515</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B223" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C223" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D223" t="n">
         <v>2014</v>
       </c>
       <c r="E223" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F223" t="n">
-        <v>121.277578340504</v>
+        <v>120.850632282833</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C224" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D224" t="n">
         <v>2014</v>
       </c>
       <c r="E224" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F224" t="n">
-        <v>43.5507200745986</v>
+        <v>43.7404334828555</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B225" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C225" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D225" t="n">
         <v>2014</v>
       </c>
       <c r="E225" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F225" t="n">
-        <v>0.118571207250546</v>
+        <v>-0.193824226910947</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C226" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D226" t="n">
         <v>2014</v>
       </c>
       <c r="E226" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F226" t="n">
-        <v>25.119639909222</v>
+        <v>26.3349562999401</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227" t="s">
+        <v>13</v>
+      </c>
+      <c r="C227" t="s">
         <v>14</v>
-      </c>
-      <c r="B227" t="s">
-        <v>15</v>
-      </c>
-      <c r="C227" t="s">
-        <v>16</v>
       </c>
       <c r="D227" t="n">
         <v>2015</v>
       </c>
       <c r="E227" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F227" t="n">
-        <v>44.3487825255756</v>
+        <v>44.7855356665619</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C228" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D228" t="n">
         <v>2015</v>
       </c>
       <c r="E228" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F228" t="n">
-        <v>96.9677463375804</v>
+        <v>97.2253849107513</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C229" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D229" t="n">
         <v>2015</v>
       </c>
       <c r="E229" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F229" t="n">
-        <v>11.9599549112123</v>
+        <v>11.9599735278583</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C230" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D230" t="n">
         <v>2015</v>
       </c>
       <c r="E230" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F230" t="n">
-        <v>38.9461205912187</v>
+        <v>39.3846451626998</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C231" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D231" t="n">
         <v>2015</v>
       </c>
       <c r="E231" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F231" t="n">
-        <v>134.749982157995</v>
+        <v>134.630008755458</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C232" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D232" t="n">
         <v>2015</v>
       </c>
       <c r="E232" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F232" t="n">
-        <v>122.162767122516</v>
+        <v>121.304618298822</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C233" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D233" t="n">
         <v>2015</v>
       </c>
       <c r="E233" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F233" t="n">
-        <v>41.3444930481942</v>
+        <v>41.5003529624434</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C234" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D234" t="n">
         <v>2015</v>
       </c>
       <c r="E234" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F234" t="n">
-        <v>-0.0214485216322217</v>
+        <v>-0.388614045907265</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C235" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D235" t="n">
         <v>2015</v>
       </c>
       <c r="E235" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F235" t="n">
-        <v>24.2956986485158</v>
+        <v>25.6158255738011</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
+        <v>12</v>
+      </c>
+      <c r="B236" t="s">
+        <v>13</v>
+      </c>
+      <c r="C236" t="s">
         <v>14</v>
-      </c>
-      <c r="B236" t="s">
-        <v>15</v>
-      </c>
-      <c r="C236" t="s">
-        <v>16</v>
       </c>
       <c r="D236" t="n">
         <v>2016</v>
       </c>
       <c r="E236" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F236" t="n">
-        <v>43.9180063958121</v>
+        <v>44.3501790895313</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C237" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D237" t="n">
         <v>2016</v>
       </c>
       <c r="E237" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F237" t="n">
-        <v>97.6186376558308</v>
+        <v>97.0046533927895</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C238" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D238" t="n">
         <v>2016</v>
       </c>
       <c r="E238" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F238" t="n">
-        <v>10.7183077075122</v>
+        <v>10.7183289979382</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C239" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D239" t="n">
         <v>2016</v>
       </c>
       <c r="E239" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F239" t="n">
-        <v>38.0862325601486</v>
+        <v>38.2695286302105</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C240" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D240" t="n">
         <v>2016</v>
       </c>
       <c r="E240" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F240" t="n">
-        <v>112.448513128619</v>
+        <v>112.33139560356</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C241" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D241" t="n">
         <v>2016</v>
       </c>
       <c r="E241" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F241" t="n">
-        <v>125.75730977684</v>
+        <v>125.125712107268</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C242" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D242" t="n">
         <v>2016</v>
       </c>
       <c r="E242" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F242" t="n">
-        <v>35.9725638029184</v>
+        <v>36.0252482044893</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C243" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D243" t="n">
         <v>2016</v>
       </c>
       <c r="E243" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F243" t="n">
-        <v>0.32834805688222</v>
+        <v>-0.0850859045666956</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C244" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D244" t="n">
         <v>2016</v>
       </c>
       <c r="E244" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F244" t="n">
-        <v>23.1239666579744</v>
+        <v>24.616222786022</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
+        <v>12</v>
+      </c>
+      <c r="B245" t="s">
+        <v>13</v>
+      </c>
+      <c r="C245" t="s">
         <v>14</v>
-      </c>
-      <c r="B245" t="s">
-        <v>15</v>
-      </c>
-      <c r="C245" t="s">
-        <v>16</v>
       </c>
       <c r="D245" t="n">
         <v>2017</v>
       </c>
       <c r="E245" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F245" t="n">
-        <v>44.1569143948416</v>
+        <v>44.6314519362547</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C246" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D246" t="n">
         <v>2017</v>
       </c>
       <c r="E246" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F246" t="n">
-        <v>95.2801045211941</v>
+        <v>94.9287016022079</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C247" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D247" t="n">
         <v>2017</v>
       </c>
       <c r="E247" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F247" t="n">
-        <v>10.3553644686229</v>
+        <v>10.356813299003</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C248" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D248" t="n">
         <v>2017</v>
       </c>
       <c r="E248" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F248" t="n">
-        <v>38.4312808735304</v>
+        <v>38.7895512412879</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C249" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D249" t="n">
         <v>2017</v>
       </c>
       <c r="E249" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F249" t="n">
-        <v>102.127788084504</v>
+        <v>102.012502683477</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B250" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C250" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D250" t="n">
         <v>2017</v>
       </c>
       <c r="E250" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F250" t="n">
-        <v>126.473648481607</v>
+        <v>125.856305679317</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C251" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D251" t="n">
         <v>2017</v>
       </c>
       <c r="E251" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F251" t="n">
-        <v>35.4986315568145</v>
+        <v>35.5428598923171</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C252" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D252" t="n">
         <v>2017</v>
       </c>
       <c r="E252" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F252" t="n">
-        <v>0.0456761735091549</v>
+        <v>-0.401773093287096</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C253" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D253" t="n">
         <v>2017</v>
       </c>
       <c r="E253" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F253" t="n">
-        <v>23.4700395210742</v>
+        <v>25.1635810589951</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
+        <v>12</v>
+      </c>
+      <c r="B254" t="s">
+        <v>13</v>
+      </c>
+      <c r="C254" t="s">
         <v>14</v>
-      </c>
-      <c r="B254" t="s">
-        <v>15</v>
-      </c>
-      <c r="C254" t="s">
-        <v>16</v>
       </c>
       <c r="D254" t="n">
         <v>2018</v>
       </c>
       <c r="E254" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F254" t="n">
-        <v>43.4606661781232</v>
+        <v>43.9126978832804</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C255" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D255" t="n">
         <v>2018</v>
       </c>
       <c r="E255" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F255" t="n">
-        <v>98.7458595045862</v>
+        <v>97.981586042921</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C256" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D256" t="n">
         <v>2018</v>
       </c>
       <c r="E256" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F256" t="n">
-        <v>10.5026193985811</v>
+        <v>10.503650969152</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C257" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D257" t="n">
         <v>2018</v>
       </c>
       <c r="E257" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F257" t="n">
-        <v>38.4522959608293</v>
+        <v>38.4400702042884</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C258" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D258" t="n">
         <v>2018</v>
       </c>
       <c r="E258" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F258" t="n">
-        <v>94.8963933433109</v>
+        <v>94.783988708557</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C259" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D259" t="n">
         <v>2018</v>
       </c>
       <c r="E259" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F259" t="n">
-        <v>125.035701317516</v>
+        <v>124.386704483577</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C260" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D260" t="n">
         <v>2018</v>
       </c>
       <c r="E260" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F260" t="n">
-        <v>33.6891888421792</v>
+        <v>33.7870117347489</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C261" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D261" t="n">
         <v>2018</v>
       </c>
       <c r="E261" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F261" t="n">
-        <v>0.706263496436295</v>
+        <v>0.225907240696161</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C262" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D262" t="n">
         <v>2018</v>
       </c>
       <c r="E262" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F262" t="n">
-        <v>23.3176411090999</v>
+        <v>25.1148832291754</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
+        <v>12</v>
+      </c>
+      <c r="B263" t="s">
+        <v>13</v>
+      </c>
+      <c r="C263" t="s">
         <v>14</v>
-      </c>
-      <c r="B263" t="s">
-        <v>15</v>
-      </c>
-      <c r="C263" t="s">
-        <v>16</v>
       </c>
       <c r="D263" t="n">
         <v>2019</v>
       </c>
       <c r="E263" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F263" t="n">
-        <v>43.7347598816888</v>
+        <v>44.1604444370543</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C264" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D264" t="n">
         <v>2019</v>
       </c>
       <c r="E264" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F264" t="n">
-        <v>95.6093794968507</v>
+        <v>94.8588678401865</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C265" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D265" t="n">
         <v>2019</v>
       </c>
       <c r="E265" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F265" t="n">
-        <v>10.3997565620938</v>
+        <v>10.4007643525211</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C266" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D266" t="n">
         <v>2019</v>
       </c>
       <c r="E266" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F266" t="n">
-        <v>37.117947523463</v>
+        <v>37.2752724853407</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C267" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D267" t="n">
         <v>2019</v>
       </c>
       <c r="E267" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F267" t="n">
-        <v>87.092163009964</v>
+        <v>86.9881670431747</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C268" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D268" t="n">
         <v>2019</v>
       </c>
       <c r="E268" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F268" t="n">
-        <v>121.800477608592</v>
+        <v>120.992310345486</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C269" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D269" t="n">
         <v>2019</v>
       </c>
       <c r="E269" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F269" t="n">
-        <v>32.9618852006074</v>
+        <v>32.9992200655733</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C270" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D270" t="n">
         <v>2019</v>
       </c>
       <c r="E270" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F270" t="n">
-        <v>0.570520431906709</v>
+        <v>0.0938000884208916</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C271" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D271" t="n">
         <v>2019</v>
       </c>
       <c r="E271" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F271" t="n">
-        <v>22.8374112899595</v>
+        <v>24.8868881484704</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
+        <v>12</v>
+      </c>
+      <c r="B272" t="s">
+        <v>13</v>
+      </c>
+      <c r="C272" t="s">
         <v>14</v>
-      </c>
-      <c r="B272" t="s">
-        <v>15</v>
-      </c>
-      <c r="C272" t="s">
-        <v>16</v>
       </c>
       <c r="D272" t="n">
         <v>2020</v>
       </c>
       <c r="E272" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F272" t="n">
-        <v>42.4629388090858</v>
+        <v>42.8698965371897</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C273" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D273" t="n">
         <v>2020</v>
       </c>
       <c r="E273" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F273" t="n">
-        <v>95.3681006538488</v>
+        <v>94.6450286259928</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C274" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D274" t="n">
         <v>2020</v>
       </c>
       <c r="E274" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F274" t="n">
-        <v>9.05321826324472</v>
+        <v>9.05702850356476</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C275" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D275" t="n">
         <v>2020</v>
       </c>
       <c r="E275" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F275" t="n">
-        <v>34.6709963726457</v>
+        <v>34.6826150051104</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C276" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D276" t="n">
         <v>2020</v>
       </c>
       <c r="E276" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F276" t="n">
-        <v>76.4730021520466</v>
+        <v>76.366006169452</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C277" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D277" t="n">
         <v>2020</v>
       </c>
       <c r="E277" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F277" t="n">
-        <v>100.545803913079</v>
+        <v>99.3011611089459</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C278" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D278" t="n">
         <v>2020</v>
       </c>
       <c r="E278" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F278" t="n">
-        <v>31.5223129707862</v>
+        <v>31.5859917188548</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C279" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D279" t="n">
         <v>2020</v>
       </c>
       <c r="E279" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F279" t="n">
-        <v>0.418826689373381</v>
+        <v>-0.0601534648585736</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C280" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D280" t="n">
         <v>2020</v>
       </c>
       <c r="E280" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F280" t="n">
-        <v>21.3311126094167</v>
+        <v>23.4919044339457</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
+        <v>12</v>
+      </c>
+      <c r="B281" t="s">
+        <v>13</v>
+      </c>
+      <c r="C281" t="s">
         <v>14</v>
-      </c>
-      <c r="B281" t="s">
-        <v>15</v>
-      </c>
-      <c r="C281" t="s">
-        <v>16</v>
       </c>
       <c r="D281" t="n">
         <v>2021</v>
       </c>
       <c r="E281" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F281" t="n">
-        <v>43.043815066131</v>
+        <v>43.4403413340811</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B282" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C282" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D282" t="n">
         <v>2021</v>
       </c>
       <c r="E282" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F282" t="n">
-        <v>100.924867665338</v>
+        <v>100.095368790166</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B283" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C283" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D283" t="n">
         <v>2021</v>
       </c>
       <c r="E283" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F283" t="n">
-        <v>8.09469389240298</v>
+        <v>8.05608757912842</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B284" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C284" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D284" t="n">
         <v>2021</v>
       </c>
       <c r="E284" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F284" t="n">
-        <v>35.2508597508233</v>
+        <v>35.2778564373776</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B285" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C285" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D285" t="n">
         <v>2021</v>
       </c>
       <c r="E285" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F285" t="n">
-        <v>79.8683777282564</v>
+        <v>79.7801621943523</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B286" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C286" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D286" t="n">
         <v>2021</v>
       </c>
       <c r="E286" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F286" t="n">
-        <v>109.007975671468</v>
+        <v>108.202332191927</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B287" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C287" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D287" t="n">
         <v>2021</v>
       </c>
       <c r="E287" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F287" t="n">
-        <v>29.7807719805805</v>
+        <v>29.9678973035863</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B288" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C288" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D288" t="n">
         <v>2021</v>
       </c>
       <c r="E288" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F288" t="n">
-        <v>0.249977614646045</v>
+        <v>-0.216106042707961</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B289" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C289" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D289" t="n">
         <v>2021</v>
       </c>
       <c r="E289" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F289" t="n">
-        <v>20.2763292984127</v>
+        <v>22.4167411800116</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
+        <v>12</v>
+      </c>
+      <c r="B290" t="s">
+        <v>13</v>
+      </c>
+      <c r="C290" t="s">
         <v>14</v>
-      </c>
-      <c r="B290" t="s">
-        <v>15</v>
-      </c>
-      <c r="C290" t="s">
-        <v>16</v>
       </c>
       <c r="D290" t="n">
         <v>2022</v>
       </c>
       <c r="E290" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F290" t="n">
-        <v>42.1935410363551</v>
+        <v>42.5870775737885</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B291" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C291" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D291" t="n">
         <v>2022</v>
       </c>
       <c r="E291" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F291" t="n">
-        <v>85.8996522914452</v>
+        <v>84.58192588348</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B292" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C292" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D292" t="n">
         <v>2022</v>
       </c>
       <c r="E292" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F292" t="n">
-        <v>7.37837403286785</v>
+        <v>7.16992472227875</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B293" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C293" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D293" t="n">
         <v>2022</v>
       </c>
       <c r="E293" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F293" t="n">
-        <v>32.980219133233</v>
+        <v>33.0017733009274</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B294" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C294" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D294" t="n">
         <v>2022</v>
       </c>
       <c r="E294" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F294" t="n">
-        <v>81.0579465811228</v>
+        <v>81.6290459686355</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B295" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C295" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D295" t="n">
         <v>2022</v>
       </c>
       <c r="E295" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F295" t="n">
-        <v>110.474528450593</v>
+        <v>109.76153063741</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B296" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C296" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D296" t="n">
         <v>2022</v>
       </c>
       <c r="E296" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F296" t="n">
-        <v>28.1931769447539</v>
+        <v>27.627773508665</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B297" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C297" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D297" t="n">
         <v>2022</v>
       </c>
       <c r="E297" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F297" t="n">
-        <v>0.571739291922666</v>
+        <v>0.116393455339269</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B298" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C298" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D298" t="n">
         <v>2022</v>
       </c>
       <c r="E298" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F298" t="n">
-        <v>20.1837958723407</v>
+        <v>22.5683176062712</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
+        <v>12</v>
+      </c>
+      <c r="B299" t="s">
+        <v>13</v>
+      </c>
+      <c r="C299" t="s">
         <v>14</v>
-      </c>
-      <c r="B299" t="s">
-        <v>15</v>
-      </c>
-      <c r="C299" t="s">
-        <v>16</v>
       </c>
       <c r="D299" t="n">
         <v>2023</v>
       </c>
       <c r="E299" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F299" t="n">
-        <v>41.4191999963011</v>
+        <v>42.0143747186113</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B300" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C300" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D300" t="n">
         <v>2023</v>
       </c>
       <c r="E300" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F300" t="n">
-        <v>81.6441796587792</v>
+        <v>81.3132943159684</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B301" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C301" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D301" t="n">
         <v>2023</v>
       </c>
       <c r="E301" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F301" t="n">
-        <v>7.26308469930605</v>
+        <v>6.84951737599927</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B302" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C302" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D302" t="n">
         <v>2023</v>
       </c>
       <c r="E302" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F302" t="n">
-        <v>33.3380128097023</v>
+        <v>32.5572470891375</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B303" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C303" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D303" t="n">
         <v>2023</v>
       </c>
       <c r="E303" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F303" t="n">
-        <v>68.726279511145</v>
+        <v>70.2049607975994</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B304" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C304" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D304" t="n">
         <v>2023</v>
       </c>
       <c r="E304" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F304" t="n">
-        <v>109.268499314331</v>
+        <v>108.545588797996</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B305" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C305" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D305" t="n">
         <v>2023</v>
       </c>
       <c r="E305" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F305" t="n">
-        <v>26.2195650319709</v>
+        <v>24.2809254429822</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B306" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C306" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D306" t="n">
         <v>2023</v>
       </c>
       <c r="E306" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F306" t="n">
-        <v>1.13802494770974</v>
+        <v>0.406313521614907</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B307" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C307" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D307" t="n">
         <v>2023</v>
       </c>
       <c r="E307" t="s">
+        <v>15</v>
+      </c>
+      <c r="F307" t="n">
+        <v>22.649720916391</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>12</v>
+      </c>
+      <c r="B308" t="s">
+        <v>13</v>
+      </c>
+      <c r="C308" t="s">
+        <v>14</v>
+      </c>
+      <c r="D308" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E308" t="s">
+        <v>15</v>
+      </c>
+      <c r="F308" t="n">
+        <v>40.9605715550603</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>12</v>
+      </c>
+      <c r="B309" t="s">
+        <v>13</v>
+      </c>
+      <c r="C309" t="s">
+        <v>16</v>
+      </c>
+      <c r="D309" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E309" t="s">
+        <v>15</v>
+      </c>
+      <c r="F309" t="n">
+        <v>85.0565983935914</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>12</v>
+      </c>
+      <c r="B310" t="s">
+        <v>13</v>
+      </c>
+      <c r="C310" t="s">
         <v>17</v>
       </c>
-      <c r="F307" t="n">
-        <v>20.074203423819</v>
+      <c r="D310" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E310" t="s">
+        <v>15</v>
+      </c>
+      <c r="F310" t="n">
+        <v>6.81377658653201</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>12</v>
+      </c>
+      <c r="B311" t="s">
+        <v>13</v>
+      </c>
+      <c r="C311" t="s">
+        <v>18</v>
+      </c>
+      <c r="D311" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E311" t="s">
+        <v>15</v>
+      </c>
+      <c r="F311" t="n">
+        <v>32.4951504447914</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>12</v>
+      </c>
+      <c r="B312" t="s">
+        <v>13</v>
+      </c>
+      <c r="C312" t="s">
+        <v>19</v>
+      </c>
+      <c r="D312" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E312" t="s">
+        <v>15</v>
+      </c>
+      <c r="F312" t="n">
+        <v>61.0814995324143</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>12</v>
+      </c>
+      <c r="B313" t="s">
+        <v>13</v>
+      </c>
+      <c r="C313" t="s">
+        <v>20</v>
+      </c>
+      <c r="D313" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E313" t="s">
+        <v>15</v>
+      </c>
+      <c r="F313" t="n">
+        <v>109.11559827901</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>12</v>
+      </c>
+      <c r="B314" t="s">
+        <v>13</v>
+      </c>
+      <c r="C314" t="s">
+        <v>21</v>
+      </c>
+      <c r="D314" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E314" t="s">
+        <v>15</v>
+      </c>
+      <c r="F314" t="n">
+        <v>20.6458777568391</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>12</v>
+      </c>
+      <c r="B315" t="s">
+        <v>13</v>
+      </c>
+      <c r="C315" t="s">
+        <v>22</v>
+      </c>
+      <c r="D315" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E315" t="s">
+        <v>15</v>
+      </c>
+      <c r="F315" t="n">
+        <v>0.349802689232048</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>12</v>
+      </c>
+      <c r="B316" t="s">
+        <v>13</v>
+      </c>
+      <c r="C316" t="s">
+        <v>23</v>
+      </c>
+      <c r="D316" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E316" t="s">
+        <v>15</v>
+      </c>
+      <c r="F316" t="n">
+        <v>21.6531599568844</v>
       </c>
     </row>
   </sheetData>

--- a/plots/countries/sectors/United Kingdom-sectors.xlsx
+++ b/plots/countries/sectors/United Kingdom-sectors.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2.1) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
